--- a/data/trans_bre/P68-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P68-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -3,26</t>
+          <t>-20,36; -3,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 7,98</t>
+          <t>-11,66; 8,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 1,91</t>
+          <t>-21,08; 1,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 27,29</t>
+          <t>-1,29; 26,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,72; -12,89</t>
+          <t>-66,87; -13,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,19; 119,96</t>
+          <t>-62,63; 142,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-73,1; 12,67</t>
+          <t>-70,68; 14,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 1446,23</t>
+          <t>-42,85; 1319,93</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 4,51</t>
+          <t>-7,63; 4,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 8,88</t>
+          <t>-5,24; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -0,32</t>
+          <t>-13,8; -0,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 4,5</t>
+          <t>-12,17; 4,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 20,0</t>
+          <t>-27,5; 19,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 45,12</t>
+          <t>-20,85; 44,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,39; -1,94</t>
+          <t>-50,91; 0,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 30,44</t>
+          <t>-57,74; 32,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 6,3</t>
+          <t>-5,24; 6,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 9,26</t>
+          <t>-4,26; 9,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 4,29</t>
+          <t>-7,78; 4,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 6,23</t>
+          <t>-4,68; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,47; 29,65</t>
+          <t>-21,67; 32,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 44,6</t>
+          <t>-16,8; 46,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 18,96</t>
+          <t>-28,16; 20,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 34,56</t>
+          <t>-19,89; 37,4</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 4,54</t>
+          <t>-10,71; 4,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 0,29</t>
+          <t>-14,23; 0,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 5,93</t>
+          <t>-9,46; 5,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 39,9</t>
+          <t>9,59; 39,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 20,14</t>
+          <t>-38,12; 18,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 1,83</t>
+          <t>-50,42; 4,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 27,36</t>
+          <t>-33,56; 25,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,33; 548,82</t>
+          <t>43,0; 552,78</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 6,61</t>
+          <t>-18,52; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 21,07</t>
+          <t>-6,71; 21,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 13,62</t>
+          <t>-9,01; 14,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 10,4</t>
+          <t>-2,09; 11,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 29,75</t>
+          <t>-56,71; 29,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 88,82</t>
+          <t>-21,73; 91,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,43; 58,21</t>
+          <t>-28,63; 67,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 54,84</t>
+          <t>-8,24; 57,89</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 16,83</t>
+          <t>-19,97; 17,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 297,81</t>
+          <t>-72,48; 318,71</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,33</t>
+          <t>-6,42; -0,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 2,94</t>
+          <t>-4,03; 2,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,44; -0,46</t>
+          <t>-7,25; -0,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,28</t>
+          <t>2,06; 14,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 1,28</t>
+          <t>-24,45; -0,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 12,92</t>
+          <t>-15,99; 13,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,73; -1,23</t>
+          <t>-27,42; -1,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,36; 105,51</t>
+          <t>10,64; 109,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P68-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P68-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>171,05%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -3,14</t>
+          <t>-20,56; -3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 8,83</t>
+          <t>-11,39; 9,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 1,71</t>
+          <t>-21,45; 1,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 26,51</t>
+          <t>-3,89; 21,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,87; -13,24</t>
+          <t>-66,64; -13,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,63; 142,95</t>
+          <t>-62,54; 146,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 14,94</t>
+          <t>-72,25; 15,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 1319,93</t>
+          <t>-35,38; 689,58</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-15,98%</t>
+          <t>-7,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 4,54</t>
+          <t>-8,22; 4,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 8,2</t>
+          <t>-5,26; 8,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,8; -0,16</t>
+          <t>-13,56; -0,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 4,69</t>
+          <t>-8,87; 4,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 19,9</t>
+          <t>-29,69; 16,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 44,06</t>
+          <t>-21,5; 43,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 0,02</t>
+          <t>-50,73; -0,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,74; 32,13</t>
+          <t>-42,89; 33,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 6,55</t>
+          <t>-5,29; 7,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 9,39</t>
+          <t>-4,44; 9,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 4,45</t>
+          <t>-8,56; 4,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,68</t>
+          <t>-3,59; 6,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 32,21</t>
+          <t>-21,16; 34,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 46,82</t>
+          <t>-17,28; 44,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 20,38</t>
+          <t>-31,02; 20,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 37,4</t>
+          <t>-16,05; 39,38</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,89</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>135,89%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 4,02</t>
+          <t>-11,16; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 0,96</t>
+          <t>-13,67; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 5,66</t>
+          <t>-9,67; 4,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 39,24</t>
+          <t>1,03; 10,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 18,42</t>
+          <t>-39,0; 21,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 4,9</t>
+          <t>-48,26; 3,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 25,75</t>
+          <t>-35,17; 21,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,0; 552,78</t>
+          <t>4,05; 56,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>4,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 7,17</t>
+          <t>-17,99; 5,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 21,35</t>
+          <t>-6,54; 20,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 14,94</t>
+          <t>-8,79; 15,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 11,06</t>
+          <t>-1,61; 10,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 29,97</t>
+          <t>-57,74; 23,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,73; 91,89</t>
+          <t>-20,28; 90,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 67,29</t>
+          <t>-27,85; 71,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 57,89</t>
+          <t>-6,98; 57,48</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,84</t>
+          <t>-3,93</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-4,85%</t>
+          <t>-20,54%</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,26; 0,0</t>
+          <t>-78,64; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 17,5</t>
+          <t>-23,6; 14,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 318,71</t>
+          <t>-76,79; 225,41</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,09</t>
+          <t>-6,81; -0,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,82</t>
+          <t>-3,79; 3,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,25; -0,5</t>
+          <t>-7,7; -0,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 14,29</t>
+          <t>-0,01; 5,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -0,08</t>
+          <t>-26,05; -1,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 13,2</t>
+          <t>-15,53; 15,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,42; -1,85</t>
+          <t>-28,19; 0,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,64; 109,12</t>
+          <t>-0,02; 30,33</t>
         </is>
       </c>
     </row>
